--- a/dist/tally_templates/SWRG.xlsx
+++ b/dist/tally_templates/SWRG.xlsx
@@ -7513,7 +7513,6 @@
       </c>
       <c r="H56" s="423">
         <f>H12</f>
-        <v>NaN</v>
       </c>
       <c r="I56" s="418" t="s">
         <v>120</v>

--- a/dist/tally_templates/SWRG.xlsx
+++ b/dist/tally_templates/SWRG.xlsx
@@ -1121,7 +1121,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3123,7 +3123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="645">
+  <cellXfs count="676">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5032,6 +5032,99 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5040,11 +5133,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5312,7 +5405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y137"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -6121,7 +6214,7 @@
       <c r="G8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="649" t="s">
         <v>106</v>
       </c>
       <c r="I8" s="16"/>
@@ -7371,7 +7464,7 @@
       <c r="G52" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="649" t="s">
         <v>106</v>
       </c>
       <c r="I52" s="16"/>
@@ -7496,27 +7589,17 @@
       <c r="Y55" s="5"/>
     </row>
     <row r="56" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="418" t="s">
-        <v>117</v>
-      </c>
+      <c r="A56" s="418"/>
       <c r="B56" s="438"/>
-      <c r="C56" s="420" t="s">
-        <v>118</v>
-      </c>
+      <c r="C56" s="420"/>
       <c r="D56" s="439"/>
       <c r="E56" s="440"/>
-      <c r="F56" s="422" t="s">
-        <v>119</v>
-      </c>
-      <c r="G56" s="441">
-        <v>-18.1</v>
-      </c>
+      <c r="F56" s="422"/>
+      <c r="G56" s="441"/>
       <c r="H56" s="423">
         <f>H12</f>
       </c>
-      <c r="I56" s="418" t="s">
-        <v>120</v>
-      </c>
+      <c r="I56" s="418"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
@@ -7535,27 +7618,15 @@
       <c r="Y56" s="5"/>
     </row>
     <row r="57" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="425" t="s">
-        <v>121</v>
-      </c>
+      <c r="A57" s="425"/>
       <c r="B57" s="442"/>
-      <c r="C57" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C57" s="442"/>
       <c r="D57" s="443"/>
       <c r="E57" s="444"/>
-      <c r="F57" s="422" t="s">
-        <v>122</v>
-      </c>
-      <c r="G57" s="422" t="s">
-        <v>122</v>
-      </c>
-      <c r="H57" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I57" s="425" t="s">
-        <v>124</v>
-      </c>
+      <c r="F57" s="422"/>
+      <c r="G57" s="422"/>
+      <c r="H57" s="445"/>
+      <c r="I57" s="425"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
@@ -7574,27 +7645,15 @@
       <c r="Y57" s="5"/>
     </row>
     <row r="58" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A58" s="425" t="s">
-        <v>125</v>
-      </c>
+      <c r="A58" s="425"/>
       <c r="B58" s="442"/>
-      <c r="C58" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C58" s="442"/>
       <c r="D58" s="443"/>
       <c r="E58" s="444"/>
-      <c r="F58" s="422" t="s">
-        <v>126</v>
-      </c>
-      <c r="G58" s="422">
-        <v>13.3</v>
-      </c>
-      <c r="H58" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I58" s="425" t="s">
-        <v>127</v>
-      </c>
+      <c r="F58" s="422"/>
+      <c r="G58" s="422"/>
+      <c r="H58" s="445"/>
+      <c r="I58" s="425"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
@@ -7613,27 +7672,15 @@
       <c r="Y58" s="5"/>
     </row>
     <row r="59" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A59" s="425" t="s">
-        <v>128</v>
-      </c>
+      <c r="A59" s="425"/>
       <c r="B59" s="442"/>
-      <c r="C59" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C59" s="442"/>
       <c r="D59" s="443"/>
       <c r="E59" s="444"/>
-      <c r="F59" s="422" t="s">
-        <v>119</v>
-      </c>
-      <c r="G59" s="422">
-        <v>-17.8</v>
-      </c>
-      <c r="H59" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I59" s="425" t="s">
-        <v>120</v>
-      </c>
+      <c r="F59" s="422"/>
+      <c r="G59" s="422"/>
+      <c r="H59" s="445"/>
+      <c r="I59" s="425"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
@@ -7652,27 +7699,15 @@
       <c r="Y59" s="5"/>
     </row>
     <row r="60" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="428" t="s">
-        <v>129</v>
-      </c>
+      <c r="A60" s="428"/>
       <c r="B60" s="446"/>
-      <c r="C60" s="446" t="s">
-        <v>118</v>
-      </c>
+      <c r="C60" s="446"/>
       <c r="D60" s="447"/>
       <c r="E60" s="448"/>
-      <c r="F60" s="449" t="s">
-        <v>119</v>
-      </c>
-      <c r="G60" s="449" t="s">
-        <v>119</v>
-      </c>
-      <c r="H60" s="450" t="s">
-        <v>123</v>
-      </c>
-      <c r="I60" s="428" t="s">
-        <v>130</v>
-      </c>
+      <c r="F60" s="449"/>
+      <c r="G60" s="449"/>
+      <c r="H60" s="450"/>
+      <c r="I60" s="428"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
@@ -7691,27 +7726,15 @@
       <c r="Y60" s="5"/>
     </row>
     <row r="61" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="418" t="s">
-        <v>131</v>
-      </c>
+      <c r="A61" s="418"/>
       <c r="B61" s="451"/>
-      <c r="C61" s="451" t="s">
-        <v>118</v>
-      </c>
+      <c r="C61" s="451"/>
       <c r="D61" s="452"/>
       <c r="E61" s="453"/>
-      <c r="F61" s="434" t="s">
-        <v>122</v>
-      </c>
-      <c r="G61" s="437" t="s">
-        <v>122</v>
-      </c>
-      <c r="H61" s="454" t="s">
-        <v>123</v>
-      </c>
-      <c r="I61" s="418" t="s">
-        <v>127</v>
-      </c>
+      <c r="F61" s="434"/>
+      <c r="G61" s="437"/>
+      <c r="H61" s="454"/>
+      <c r="I61" s="418"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
@@ -7730,27 +7753,15 @@
       <c r="Y61" s="5"/>
     </row>
     <row r="62" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="425" t="s">
-        <v>132</v>
-      </c>
+      <c r="A62" s="425"/>
       <c r="B62" s="455"/>
-      <c r="C62" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C62" s="442"/>
       <c r="D62" s="443"/>
       <c r="E62" s="444"/>
-      <c r="F62" s="422" t="s">
-        <v>122</v>
-      </c>
-      <c r="G62" s="422">
-        <v>13.9</v>
-      </c>
-      <c r="H62" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I62" s="425" t="s">
-        <v>124</v>
-      </c>
+      <c r="F62" s="422"/>
+      <c r="G62" s="422"/>
+      <c r="H62" s="445"/>
+      <c r="I62" s="425"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
@@ -7769,27 +7780,15 @@
       <c r="Y62" s="5"/>
     </row>
     <row r="63" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="425" t="s">
-        <v>133</v>
-      </c>
+      <c r="A63" s="425"/>
       <c r="B63" s="455"/>
-      <c r="C63" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C63" s="442"/>
       <c r="D63" s="443"/>
       <c r="E63" s="444"/>
-      <c r="F63" s="422" t="s">
-        <v>134</v>
-      </c>
-      <c r="G63" s="422" t="s">
-        <v>134</v>
-      </c>
-      <c r="H63" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I63" s="425" t="s">
-        <v>124</v>
-      </c>
+      <c r="F63" s="422"/>
+      <c r="G63" s="422"/>
+      <c r="H63" s="445"/>
+      <c r="I63" s="425"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
@@ -7808,27 +7807,15 @@
       <c r="Y63" s="5"/>
     </row>
     <row r="64" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="425" t="s">
-        <v>135</v>
-      </c>
+      <c r="A64" s="425"/>
       <c r="B64" s="455"/>
-      <c r="C64" s="442" t="s">
-        <v>118</v>
-      </c>
+      <c r="C64" s="442"/>
       <c r="D64" s="443"/>
       <c r="E64" s="444"/>
-      <c r="F64" s="422" t="s">
-        <v>122</v>
-      </c>
-      <c r="G64" s="422">
-        <v>14.1</v>
-      </c>
-      <c r="H64" s="445" t="s">
-        <v>123</v>
-      </c>
-      <c r="I64" s="425" t="s">
-        <v>124</v>
-      </c>
+      <c r="F64" s="422"/>
+      <c r="G64" s="422"/>
+      <c r="H64" s="445"/>
+      <c r="I64" s="425"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
@@ -7847,27 +7834,15 @@
       <c r="Y64" s="5"/>
     </row>
     <row r="65" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="428" t="s">
-        <v>136</v>
-      </c>
+      <c r="A65" s="428"/>
       <c r="B65" s="429"/>
-      <c r="C65" s="446" t="s">
-        <v>118</v>
-      </c>
+      <c r="C65" s="446"/>
       <c r="D65" s="447"/>
       <c r="E65" s="448"/>
-      <c r="F65" s="449" t="s">
-        <v>137</v>
-      </c>
-      <c r="G65" s="449" t="s">
-        <v>137</v>
-      </c>
-      <c r="H65" s="450" t="s">
-        <v>123</v>
-      </c>
-      <c r="I65" s="428" t="s">
-        <v>124</v>
-      </c>
+      <c r="F65" s="449"/>
+      <c r="G65" s="449"/>
+      <c r="H65" s="450"/>
+      <c r="I65" s="428"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
@@ -7886,27 +7861,15 @@
       <c r="Y65" s="5"/>
     </row>
     <row r="66" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="418" t="s">
-        <v>138</v>
-      </c>
+      <c r="A66" s="418"/>
       <c r="B66" s="433"/>
-      <c r="C66" s="451" t="s">
-        <v>118</v>
-      </c>
+      <c r="C66" s="451"/>
       <c r="D66" s="452"/>
       <c r="E66" s="453"/>
-      <c r="F66" s="434" t="s">
-        <v>122</v>
-      </c>
-      <c r="G66" s="437">
-        <v>14.1</v>
-      </c>
-      <c r="H66" s="454" t="s">
-        <v>123</v>
-      </c>
-      <c r="I66" s="418" t="s">
-        <v>127</v>
-      </c>
+      <c r="F66" s="434"/>
+      <c r="G66" s="437"/>
+      <c r="H66" s="454"/>
+      <c r="I66" s="418"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
@@ -8765,7 +8728,7 @@
       <c r="G96" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="16" t="s">
+      <c r="H96" s="649" t="s">
         <v>106</v>
       </c>
       <c r="I96" s="16"/>
@@ -10039,7 +10002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10840,7 +10803,7 @@
       <c r="A8" s="200" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="202" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="200"/>
@@ -10852,7 +10815,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="197"/>
-      <c r="J8" s="197" t="s">
+      <c r="J8" s="202" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="197"/>
@@ -10903,7 +10866,7 @@
       <c r="X9" s="145"/>
       <c r="Y9" s="145"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="206" t="s">
         <v>11</v>
       </c>
@@ -10944,7 +10907,7 @@
       <c r="X10" s="145"/>
       <c r="Y10" s="145"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="210"/>
       <c r="B11" s="210"/>
       <c r="C11" s="279"/>
@@ -11790,7 +11753,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -12147,7 +12110,7 @@
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="645" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5"/>
@@ -12156,14 +12119,14 @@
       <c r="F4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="14"/>
+      <c r="G4" s="646"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="5"/>
       <c r="K4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="15"/>
+      <c r="L4" s="647"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
@@ -12209,21 +12172,21 @@
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="646"/>
       <c r="C6" s="5"/>
       <c r="D6" s="11"/>
       <c r="E6" s="19"/>
       <c r="F6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="646"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="5"/>
       <c r="K6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="648" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="20"/>
@@ -14732,7 +14695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -15416,7 +15379,7 @@
       <c r="O6" s="276" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="193"/>
+      <c r="P6" s="674"/>
       <c r="Q6" s="193"/>
       <c r="R6" s="124" t="str">
         <f>'Final Work'!G4</f>
@@ -15488,7 +15451,7 @@
       <c r="A8" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="144"/>
+      <c r="B8" s="675"/>
       <c r="C8" s="144"/>
       <c r="D8" s="477" t="s">
         <v>61</v>
@@ -15506,7 +15469,7 @@
       <c r="O8" s="477" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="144"/>
+      <c r="P8" s="675"/>
       <c r="Q8" s="144"/>
       <c r="R8" s="476">
         <f>'Final Work'!G6</f>
@@ -15523,7 +15486,7 @@
       </c>
       <c r="Z8" s="476"/>
       <c r="AA8" s="476"/>
-      <c r="AB8" s="476" t="s">
+      <c r="AB8" s="675" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="476"/>
@@ -20777,7 +20740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -21582,13 +21545,13 @@
       <c r="G6" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="197"/>
+      <c r="H6" s="202"/>
       <c r="I6" s="197"/>
       <c r="J6" s="145"/>
       <c r="K6" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="201"/>
+      <c r="L6" s="658"/>
       <c r="M6" s="197"/>
       <c r="N6" s="5"/>
       <c r="O6" s="145"/>
@@ -21634,7 +21597,7 @@
       <c r="A8" s="200" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="659" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="145"/>
@@ -21644,13 +21607,13 @@
       <c r="G8" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="197"/>
+      <c r="H8" s="202"/>
       <c r="I8" s="197"/>
       <c r="J8" s="145"/>
       <c r="K8" s="200" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="197"/>
+      <c r="L8" s="202"/>
       <c r="M8" s="197"/>
       <c r="N8" s="145"/>
       <c r="O8" s="145"/>
@@ -21692,7 +21655,7 @@
       <c r="X9" s="145"/>
       <c r="Y9" s="145"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="203" t="s">
         <v>41</v>
       </c>
@@ -21737,7 +21700,7 @@
       <c r="X10" s="145"/>
       <c r="Y10" s="145"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="207"/>
       <c r="B11" s="208"/>
       <c r="C11" s="209"/>
@@ -21772,14 +21735,14 @@
       <c r="C12" s="213"/>
       <c r="D12" s="214"/>
       <c r="E12" s="215"/>
-      <c r="F12" s="216"/>
+      <c r="F12" s="660"/>
       <c r="G12" s="217"/>
       <c r="H12" s="218"/>
       <c r="I12" s="219"/>
       <c r="J12" s="220"/>
       <c r="K12" s="221"/>
       <c r="L12" s="221"/>
-      <c r="M12" s="222"/>
+      <c r="M12" s="661"/>
       <c r="N12" s="145"/>
       <c r="O12" s="145"/>
       <c r="P12" s="145"/>
@@ -21799,14 +21762,14 @@
       <c r="C13" s="213"/>
       <c r="D13" s="212"/>
       <c r="E13" s="224"/>
-      <c r="F13" s="225"/>
+      <c r="F13" s="213"/>
       <c r="G13" s="223"/>
       <c r="H13" s="226"/>
       <c r="I13" s="227"/>
       <c r="J13" s="228"/>
       <c r="K13" s="223"/>
       <c r="L13" s="223"/>
-      <c r="M13" s="229"/>
+      <c r="M13" s="662"/>
       <c r="N13" s="145"/>
       <c r="O13" s="145"/>
       <c r="P13" s="145"/>
@@ -21826,14 +21789,14 @@
       <c r="C14" s="213"/>
       <c r="D14" s="230"/>
       <c r="E14" s="231"/>
-      <c r="F14" s="232"/>
+      <c r="F14" s="663"/>
       <c r="G14" s="221"/>
       <c r="H14" s="226"/>
       <c r="I14" s="227"/>
       <c r="J14" s="228"/>
       <c r="K14" s="223"/>
       <c r="L14" s="223"/>
-      <c r="M14" s="229"/>
+      <c r="M14" s="662"/>
       <c r="N14" s="145"/>
       <c r="O14" s="145"/>
       <c r="P14" s="145"/>
@@ -21853,14 +21816,14 @@
       <c r="C15" s="213"/>
       <c r="D15" s="212"/>
       <c r="E15" s="224"/>
-      <c r="F15" s="225"/>
+      <c r="F15" s="213"/>
       <c r="G15" s="223"/>
       <c r="H15" s="226"/>
       <c r="I15" s="227"/>
       <c r="J15" s="228"/>
       <c r="K15" s="223"/>
       <c r="L15" s="223"/>
-      <c r="M15" s="229"/>
+      <c r="M15" s="662"/>
       <c r="N15" s="145"/>
       <c r="O15" s="145"/>
       <c r="P15" s="145"/>
@@ -21880,14 +21843,14 @@
       <c r="C16" s="213"/>
       <c r="D16" s="230"/>
       <c r="E16" s="231"/>
-      <c r="F16" s="232"/>
+      <c r="F16" s="663"/>
       <c r="G16" s="221"/>
       <c r="H16" s="226"/>
       <c r="I16" s="227"/>
       <c r="J16" s="228"/>
       <c r="K16" s="223"/>
       <c r="L16" s="223"/>
-      <c r="M16" s="229"/>
+      <c r="M16" s="662"/>
       <c r="N16" s="145"/>
       <c r="O16" s="145"/>
       <c r="P16" s="145"/>
@@ -21907,14 +21870,14 @@
       <c r="C17" s="213"/>
       <c r="D17" s="233"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="234"/>
+      <c r="F17" s="258"/>
       <c r="G17" s="235"/>
       <c r="H17" s="226"/>
       <c r="I17" s="227"/>
       <c r="J17" s="228"/>
       <c r="K17" s="223"/>
       <c r="L17" s="223"/>
-      <c r="M17" s="229"/>
+      <c r="M17" s="662"/>
       <c r="N17" s="145"/>
       <c r="O17" s="145"/>
       <c r="P17" s="145"/>
@@ -21934,14 +21897,14 @@
       <c r="C18" s="213"/>
       <c r="D18" s="212"/>
       <c r="E18" s="224"/>
-      <c r="F18" s="225"/>
+      <c r="F18" s="213"/>
       <c r="G18" s="223"/>
       <c r="H18" s="226"/>
       <c r="I18" s="227"/>
       <c r="J18" s="228"/>
       <c r="K18" s="223"/>
       <c r="L18" s="223"/>
-      <c r="M18" s="229"/>
+      <c r="M18" s="662"/>
       <c r="N18" s="145"/>
       <c r="O18" s="145"/>
       <c r="P18" s="145"/>
@@ -21961,14 +21924,14 @@
       <c r="C19" s="213"/>
       <c r="D19" s="212"/>
       <c r="E19" s="224"/>
-      <c r="F19" s="225"/>
+      <c r="F19" s="213"/>
       <c r="G19" s="223"/>
       <c r="H19" s="226"/>
       <c r="I19" s="227"/>
       <c r="J19" s="228"/>
       <c r="K19" s="223"/>
       <c r="L19" s="223"/>
-      <c r="M19" s="229"/>
+      <c r="M19" s="662"/>
       <c r="N19" s="145"/>
       <c r="O19" s="145"/>
       <c r="P19" s="145"/>
@@ -21988,14 +21951,14 @@
       <c r="C20" s="238"/>
       <c r="D20" s="237"/>
       <c r="E20" s="196"/>
-      <c r="F20" s="239"/>
+      <c r="F20" s="238"/>
       <c r="G20" s="236"/>
       <c r="H20" s="240"/>
       <c r="I20" s="241"/>
       <c r="J20" s="242"/>
       <c r="K20" s="236"/>
       <c r="L20" s="236"/>
-      <c r="M20" s="243"/>
+      <c r="M20" s="664"/>
       <c r="N20" s="145"/>
       <c r="O20" s="145"/>
       <c r="P20" s="145"/>
@@ -22015,14 +21978,14 @@
       <c r="C21" s="213"/>
       <c r="D21" s="212"/>
       <c r="E21" s="224"/>
-      <c r="F21" s="225"/>
+      <c r="F21" s="213"/>
       <c r="G21" s="223"/>
       <c r="H21" s="226"/>
       <c r="I21" s="227"/>
       <c r="J21" s="228"/>
       <c r="K21" s="223"/>
       <c r="L21" s="223"/>
-      <c r="M21" s="229"/>
+      <c r="M21" s="662"/>
       <c r="N21" s="145"/>
       <c r="O21" s="145"/>
       <c r="P21" s="145"/>
@@ -22042,14 +22005,14 @@
       <c r="C22" s="213"/>
       <c r="D22" s="212"/>
       <c r="E22" s="224"/>
-      <c r="F22" s="225"/>
+      <c r="F22" s="213"/>
       <c r="G22" s="223"/>
       <c r="H22" s="226"/>
       <c r="I22" s="227"/>
       <c r="J22" s="228"/>
       <c r="K22" s="223"/>
       <c r="L22" s="223"/>
-      <c r="M22" s="229"/>
+      <c r="M22" s="662"/>
       <c r="N22" s="145"/>
       <c r="O22" s="145"/>
       <c r="P22" s="145"/>
@@ -22763,7 +22726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -23564,7 +23527,7 @@
       <c r="A8" s="200" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="202" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="200"/>
@@ -23576,7 +23539,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="197"/>
-      <c r="J8" s="197" t="s">
+      <c r="J8" s="202" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="197"/>
@@ -23627,7 +23590,7 @@
       <c r="X9" s="145"/>
       <c r="Y9" s="145"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="203" t="s">
         <v>11</v>
       </c>
@@ -23668,7 +23631,7 @@
       <c r="X10" s="145"/>
       <c r="Y10" s="145"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="207"/>
       <c r="B11" s="207"/>
       <c r="C11" s="279"/>
@@ -23698,32 +23661,18 @@
       <c r="Y11" s="145"/>
     </row>
     <row r="12" ht="18.95" customHeight="1" spans="1:25" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="282" t="s">
-        <v>70</v>
-      </c>
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="282"/>
       <c r="D12" s="283"/>
       <c r="E12" s="284"/>
-      <c r="F12" s="282" t="s">
-        <v>71</v>
-      </c>
+      <c r="F12" s="282"/>
       <c r="G12" s="283"/>
       <c r="H12" s="283"/>
       <c r="I12" s="284"/>
-      <c r="J12" s="285">
-        <v>1</v>
-      </c>
-      <c r="K12" s="285" t="s">
-        <v>52</v>
-      </c>
-      <c r="L12" s="286" t="s">
-        <v>72</v>
-      </c>
+      <c r="J12" s="285"/>
+      <c r="K12" s="285"/>
+      <c r="L12" s="286"/>
       <c r="M12" s="287"/>
       <c r="N12" s="287"/>
       <c r="O12" s="287"/>
@@ -23739,32 +23688,18 @@
       <c r="Y12" s="145"/>
     </row>
     <row r="13" ht="18.95" customHeight="1" spans="1:25" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="289" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="289" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="161" t="s">
-        <v>74</v>
-      </c>
+      <c r="A13" s="289"/>
+      <c r="B13" s="289"/>
+      <c r="C13" s="161"/>
       <c r="D13" s="290"/>
       <c r="E13" s="166"/>
-      <c r="F13" s="183" t="s">
-        <v>71</v>
-      </c>
+      <c r="F13" s="183"/>
       <c r="G13" s="57"/>
       <c r="H13" s="57"/>
       <c r="I13" s="59"/>
-      <c r="J13" s="56">
-        <v>1</v>
-      </c>
-      <c r="K13" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="180" t="s">
-        <v>75</v>
-      </c>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="180"/>
       <c r="M13" s="181"/>
       <c r="N13" s="181"/>
       <c r="O13" s="181"/>
@@ -24540,7 +24475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -25207,11 +25142,11 @@
       <c r="A6" s="149" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="150"/>
+      <c r="B6" s="648"/>
       <c r="C6" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="649"/>
       <c r="E6" s="16"/>
       <c r="F6" s="10"/>
       <c r="G6" s="151" t="s">
@@ -25270,17 +25205,17 @@
       <c r="A8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="153"/>
+      <c r="B8" s="649"/>
       <c r="C8" s="149" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="16"/>
+      <c r="D8" s="649"/>
       <c r="E8" s="16"/>
       <c r="F8" s="149"/>
       <c r="G8" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="648"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -25416,7 +25351,7 @@
     <row r="13" ht="18" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="158"/>
       <c r="B13" s="159"/>
-      <c r="C13" s="160"/>
+      <c r="C13" s="650"/>
       <c r="D13" s="160"/>
       <c r="E13" s="160"/>
       <c r="F13" s="160"/>
@@ -25443,7 +25378,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="161"/>
       <c r="B14" s="162"/>
-      <c r="C14" s="163"/>
+      <c r="C14" s="651"/>
       <c r="D14" s="164"/>
       <c r="E14" s="164"/>
       <c r="F14" s="164"/>
@@ -25470,7 +25405,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="161"/>
       <c r="B15" s="166"/>
-      <c r="C15" s="163"/>
+      <c r="C15" s="651"/>
       <c r="D15" s="164"/>
       <c r="E15" s="164"/>
       <c r="F15" s="164"/>
@@ -25497,7 +25432,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="161"/>
       <c r="B16" s="166"/>
-      <c r="C16" s="163"/>
+      <c r="C16" s="651"/>
       <c r="D16" s="164"/>
       <c r="E16" s="164"/>
       <c r="F16" s="164"/>
@@ -25524,7 +25459,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="167"/>
       <c r="B17" s="168"/>
-      <c r="C17" s="169"/>
+      <c r="C17" s="652"/>
       <c r="D17" s="170"/>
       <c r="E17" s="170"/>
       <c r="F17" s="170"/>
@@ -25551,7 +25486,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="172"/>
       <c r="B18" s="173"/>
-      <c r="C18" s="174"/>
+      <c r="C18" s="653"/>
       <c r="D18" s="174"/>
       <c r="E18" s="174"/>
       <c r="F18" s="174"/>
@@ -25578,7 +25513,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="175"/>
       <c r="B19" s="162"/>
-      <c r="C19" s="176"/>
+      <c r="C19" s="654"/>
       <c r="D19" s="176"/>
       <c r="E19" s="176"/>
       <c r="F19" s="176"/>
@@ -25605,7 +25540,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="161"/>
       <c r="B20" s="162"/>
-      <c r="C20" s="176"/>
+      <c r="C20" s="654"/>
       <c r="D20" s="176"/>
       <c r="E20" s="176"/>
       <c r="F20" s="176"/>
@@ -25632,7 +25567,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="177"/>
       <c r="B21" s="162"/>
-      <c r="C21" s="176"/>
+      <c r="C21" s="654"/>
       <c r="D21" s="176"/>
       <c r="E21" s="176"/>
       <c r="F21" s="176"/>
@@ -25659,7 +25594,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="178"/>
       <c r="B22" s="168"/>
-      <c r="C22" s="169"/>
+      <c r="C22" s="652"/>
       <c r="D22" s="170"/>
       <c r="E22" s="170"/>
       <c r="F22" s="170"/>
@@ -25686,7 +25621,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="179"/>
       <c r="B23" s="59"/>
-      <c r="C23" s="180"/>
+      <c r="C23" s="655"/>
       <c r="D23" s="181"/>
       <c r="E23" s="181"/>
       <c r="F23" s="181"/>
@@ -25713,7 +25648,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="183"/>
       <c r="B24" s="166"/>
-      <c r="C24" s="180"/>
+      <c r="C24" s="655"/>
       <c r="D24" s="181"/>
       <c r="E24" s="181"/>
       <c r="F24" s="181"/>
@@ -25740,7 +25675,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="184"/>
       <c r="B25" s="166"/>
-      <c r="C25" s="163"/>
+      <c r="C25" s="651"/>
       <c r="D25" s="164"/>
       <c r="E25" s="164"/>
       <c r="F25" s="164"/>
@@ -25767,7 +25702,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="161"/>
       <c r="B26" s="166"/>
-      <c r="C26" s="163"/>
+      <c r="C26" s="651"/>
       <c r="D26" s="164"/>
       <c r="E26" s="164"/>
       <c r="F26" s="164"/>
@@ -25794,7 +25729,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="167"/>
       <c r="B27" s="168"/>
-      <c r="C27" s="169"/>
+      <c r="C27" s="652"/>
       <c r="D27" s="170"/>
       <c r="E27" s="170"/>
       <c r="F27" s="170"/>
@@ -25821,7 +25756,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="59"/>
-      <c r="C28" s="180"/>
+      <c r="C28" s="655"/>
       <c r="D28" s="181"/>
       <c r="E28" s="181"/>
       <c r="F28" s="181"/>
@@ -25848,7 +25783,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="161"/>
       <c r="B29" s="166"/>
-      <c r="C29" s="163"/>
+      <c r="C29" s="651"/>
       <c r="D29" s="164"/>
       <c r="E29" s="164"/>
       <c r="F29" s="164"/>
@@ -25875,7 +25810,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="161"/>
       <c r="B30" s="166"/>
-      <c r="C30" s="163"/>
+      <c r="C30" s="651"/>
       <c r="D30" s="164"/>
       <c r="E30" s="164"/>
       <c r="F30" s="164"/>
@@ -25902,7 +25837,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="161"/>
       <c r="B31" s="166"/>
-      <c r="C31" s="163"/>
+      <c r="C31" s="651"/>
       <c r="D31" s="164"/>
       <c r="E31" s="164"/>
       <c r="F31" s="164"/>
@@ -25929,7 +25864,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="184"/>
       <c r="B32" s="168"/>
-      <c r="C32" s="169"/>
+      <c r="C32" s="652"/>
       <c r="D32" s="170"/>
       <c r="E32" s="170"/>
       <c r="F32" s="170"/>
@@ -25956,7 +25891,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
       <c r="B33" s="59"/>
-      <c r="C33" s="180"/>
+      <c r="C33" s="655"/>
       <c r="D33" s="181"/>
       <c r="E33" s="181"/>
       <c r="F33" s="181"/>
@@ -25983,7 +25918,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="161"/>
       <c r="B34" s="162"/>
-      <c r="C34" s="176"/>
+      <c r="C34" s="654"/>
       <c r="D34" s="176"/>
       <c r="E34" s="176"/>
       <c r="F34" s="176"/>
@@ -26010,7 +25945,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="185"/>
       <c r="B35" s="166"/>
-      <c r="C35" s="186"/>
+      <c r="C35" s="656"/>
       <c r="D35" s="164"/>
       <c r="E35" s="164"/>
       <c r="F35" s="164"/>
@@ -26037,7 +25972,7 @@
     <row r="36" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="187"/>
       <c r="B36" s="166"/>
-      <c r="C36" s="180"/>
+      <c r="C36" s="655"/>
       <c r="D36" s="181"/>
       <c r="E36" s="181"/>
       <c r="F36" s="181"/>
@@ -26064,7 +25999,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="188"/>
       <c r="B37" s="168"/>
-      <c r="C37" s="169"/>
+      <c r="C37" s="652"/>
       <c r="D37" s="170"/>
       <c r="E37" s="170"/>
       <c r="F37" s="170"/>
@@ -26091,7 +26026,7 @@
     <row r="38" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="189"/>
       <c r="B38" s="59"/>
-      <c r="C38" s="190"/>
+      <c r="C38" s="657"/>
       <c r="D38" s="191"/>
       <c r="E38" s="191"/>
       <c r="F38" s="191"/>
@@ -26118,7 +26053,7 @@
     <row r="39" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="187"/>
       <c r="B39" s="166"/>
-      <c r="C39" s="163"/>
+      <c r="C39" s="651"/>
       <c r="D39" s="164"/>
       <c r="E39" s="164"/>
       <c r="F39" s="164"/>
@@ -26145,7 +26080,7 @@
     <row r="40" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="187"/>
       <c r="B40" s="166"/>
-      <c r="C40" s="163"/>
+      <c r="C40" s="651"/>
       <c r="D40" s="164"/>
       <c r="E40" s="164"/>
       <c r="F40" s="164"/>
@@ -26172,7 +26107,7 @@
     <row r="41" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="161"/>
       <c r="B41" s="166"/>
-      <c r="C41" s="163"/>
+      <c r="C41" s="651"/>
       <c r="D41" s="164"/>
       <c r="E41" s="164"/>
       <c r="F41" s="164"/>
@@ -26199,7 +26134,7 @@
     <row r="42" ht="18" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="161"/>
       <c r="B42" s="59"/>
-      <c r="C42" s="163"/>
+      <c r="C42" s="651"/>
       <c r="D42" s="164"/>
       <c r="E42" s="164"/>
       <c r="F42" s="164"/>
@@ -26469,7 +26404,7 @@
       <c r="Y51" s="145"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -26509,6 +26444,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -26517,7 +26454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -27322,13 +27259,13 @@
       <c r="G6" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="197"/>
+      <c r="H6" s="202"/>
       <c r="I6" s="197"/>
       <c r="J6" s="145"/>
       <c r="K6" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="201"/>
+      <c r="L6" s="658"/>
       <c r="M6" s="197"/>
       <c r="N6" s="5"/>
       <c r="O6" s="145"/>
@@ -27374,7 +27311,7 @@
       <c r="A8" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="659" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="291"/>
@@ -27384,13 +27321,13 @@
       <c r="G8" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="197"/>
+      <c r="H8" s="202"/>
       <c r="I8" s="197"/>
       <c r="J8" s="145"/>
       <c r="K8" s="200" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="197"/>
+      <c r="L8" s="202"/>
       <c r="M8" s="197"/>
       <c r="N8" s="145"/>
       <c r="O8" s="145"/>
@@ -27432,7 +27369,7 @@
       <c r="X9" s="145"/>
       <c r="Y9" s="145"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="292" t="s">
         <v>41</v>
       </c>
@@ -27477,7 +27414,7 @@
       <c r="X10" s="145"/>
       <c r="Y10" s="145"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="207"/>
       <c r="B11" s="208"/>
       <c r="C11" s="209"/>
@@ -27512,14 +27449,14 @@
       <c r="C12" s="217"/>
       <c r="D12" s="214"/>
       <c r="E12" s="215"/>
-      <c r="F12" s="293"/>
+      <c r="F12" s="665"/>
       <c r="G12" s="217"/>
       <c r="H12" s="294"/>
       <c r="I12" s="295"/>
       <c r="J12" s="296"/>
       <c r="K12" s="217"/>
       <c r="L12" s="217"/>
-      <c r="M12" s="297"/>
+      <c r="M12" s="666"/>
       <c r="N12" s="145"/>
       <c r="O12" s="145"/>
       <c r="P12" s="145"/>
@@ -27539,14 +27476,14 @@
       <c r="C13" s="213"/>
       <c r="D13" s="212"/>
       <c r="E13" s="224"/>
-      <c r="F13" s="298"/>
+      <c r="F13" s="667"/>
       <c r="G13" s="223"/>
       <c r="H13" s="226"/>
       <c r="I13" s="227"/>
       <c r="J13" s="228"/>
       <c r="K13" s="223"/>
       <c r="L13" s="223"/>
-      <c r="M13" s="299"/>
+      <c r="M13" s="668"/>
       <c r="N13" s="145"/>
       <c r="O13" s="145"/>
       <c r="P13" s="145"/>
@@ -27566,14 +27503,14 @@
       <c r="C14" s="213"/>
       <c r="D14" s="212"/>
       <c r="E14" s="224"/>
-      <c r="F14" s="298"/>
+      <c r="F14" s="667"/>
       <c r="G14" s="223"/>
       <c r="H14" s="226"/>
       <c r="I14" s="227"/>
       <c r="J14" s="228"/>
       <c r="K14" s="223"/>
       <c r="L14" s="223"/>
-      <c r="M14" s="299"/>
+      <c r="M14" s="668"/>
       <c r="N14" s="145"/>
       <c r="O14" s="145"/>
       <c r="P14" s="145"/>
@@ -27593,14 +27530,14 @@
       <c r="C15" s="213"/>
       <c r="D15" s="212"/>
       <c r="E15" s="224"/>
-      <c r="F15" s="298"/>
+      <c r="F15" s="667"/>
       <c r="G15" s="223"/>
       <c r="H15" s="226"/>
       <c r="I15" s="227"/>
       <c r="J15" s="228"/>
       <c r="K15" s="223"/>
       <c r="L15" s="223"/>
-      <c r="M15" s="299"/>
+      <c r="M15" s="668"/>
       <c r="N15" s="145"/>
       <c r="O15" s="145"/>
       <c r="P15" s="145"/>
@@ -27620,14 +27557,14 @@
       <c r="C16" s="213"/>
       <c r="D16" s="212"/>
       <c r="E16" s="224"/>
-      <c r="F16" s="298"/>
+      <c r="F16" s="667"/>
       <c r="G16" s="223"/>
       <c r="H16" s="226"/>
       <c r="I16" s="227"/>
       <c r="J16" s="228"/>
       <c r="K16" s="223"/>
       <c r="L16" s="223"/>
-      <c r="M16" s="299"/>
+      <c r="M16" s="668"/>
       <c r="N16" s="145"/>
       <c r="O16" s="145"/>
       <c r="P16" s="145"/>
@@ -27647,14 +27584,14 @@
       <c r="C17" s="213"/>
       <c r="D17" s="212"/>
       <c r="E17" s="224"/>
-      <c r="F17" s="298"/>
+      <c r="F17" s="667"/>
       <c r="G17" s="223"/>
       <c r="H17" s="226"/>
       <c r="I17" s="227"/>
       <c r="J17" s="228"/>
       <c r="K17" s="223"/>
       <c r="L17" s="223"/>
-      <c r="M17" s="299"/>
+      <c r="M17" s="668"/>
       <c r="N17" s="145"/>
       <c r="O17" s="145"/>
       <c r="P17" s="145"/>
@@ -27674,14 +27611,14 @@
       <c r="C18" s="213"/>
       <c r="D18" s="212"/>
       <c r="E18" s="224"/>
-      <c r="F18" s="298"/>
+      <c r="F18" s="667"/>
       <c r="G18" s="223"/>
       <c r="H18" s="226"/>
       <c r="I18" s="227"/>
       <c r="J18" s="228"/>
       <c r="K18" s="223"/>
       <c r="L18" s="223"/>
-      <c r="M18" s="299"/>
+      <c r="M18" s="668"/>
       <c r="N18" s="145"/>
       <c r="O18" s="145"/>
       <c r="P18" s="145"/>
@@ -27701,14 +27638,14 @@
       <c r="C19" s="213"/>
       <c r="D19" s="212"/>
       <c r="E19" s="224"/>
-      <c r="F19" s="298"/>
+      <c r="F19" s="667"/>
       <c r="G19" s="223"/>
       <c r="H19" s="226"/>
       <c r="I19" s="227"/>
       <c r="J19" s="228"/>
       <c r="K19" s="223"/>
       <c r="L19" s="223"/>
-      <c r="M19" s="299"/>
+      <c r="M19" s="668"/>
       <c r="N19" s="145"/>
       <c r="O19" s="145"/>
       <c r="P19" s="145"/>
@@ -27728,14 +27665,14 @@
       <c r="C20" s="213"/>
       <c r="D20" s="212"/>
       <c r="E20" s="224"/>
-      <c r="F20" s="298"/>
+      <c r="F20" s="667"/>
       <c r="G20" s="223"/>
       <c r="H20" s="226"/>
       <c r="I20" s="227"/>
       <c r="J20" s="228"/>
       <c r="K20" s="223"/>
       <c r="L20" s="223"/>
-      <c r="M20" s="299"/>
+      <c r="M20" s="668"/>
       <c r="N20" s="145"/>
       <c r="O20" s="145"/>
       <c r="P20" s="145"/>
@@ -27755,14 +27692,14 @@
       <c r="C21" s="213"/>
       <c r="D21" s="212"/>
       <c r="E21" s="224"/>
-      <c r="F21" s="298"/>
+      <c r="F21" s="667"/>
       <c r="G21" s="223"/>
       <c r="H21" s="226"/>
       <c r="I21" s="227"/>
       <c r="J21" s="228"/>
       <c r="K21" s="223"/>
       <c r="L21" s="223"/>
-      <c r="M21" s="299"/>
+      <c r="M21" s="668"/>
       <c r="N21" s="145"/>
       <c r="O21" s="145"/>
       <c r="P21" s="145"/>
@@ -27782,14 +27719,14 @@
       <c r="C22" s="213"/>
       <c r="D22" s="212"/>
       <c r="E22" s="224"/>
-      <c r="F22" s="298"/>
+      <c r="F22" s="667"/>
       <c r="G22" s="223"/>
       <c r="H22" s="226"/>
       <c r="I22" s="227"/>
       <c r="J22" s="228"/>
       <c r="K22" s="223"/>
       <c r="L22" s="223"/>
-      <c r="M22" s="299"/>
+      <c r="M22" s="668"/>
       <c r="N22" s="145"/>
       <c r="O22" s="145"/>
       <c r="P22" s="145"/>
@@ -27809,14 +27746,14 @@
       <c r="C23" s="213"/>
       <c r="D23" s="212"/>
       <c r="E23" s="224"/>
-      <c r="F23" s="298"/>
+      <c r="F23" s="667"/>
       <c r="G23" s="223"/>
       <c r="H23" s="226"/>
       <c r="I23" s="227"/>
       <c r="J23" s="228"/>
       <c r="K23" s="223"/>
       <c r="L23" s="223"/>
-      <c r="M23" s="299"/>
+      <c r="M23" s="668"/>
       <c r="N23" s="145"/>
       <c r="O23" s="145"/>
       <c r="P23" s="145"/>
@@ -27836,14 +27773,14 @@
       <c r="C24" s="213"/>
       <c r="D24" s="212"/>
       <c r="E24" s="224"/>
-      <c r="F24" s="298"/>
+      <c r="F24" s="667"/>
       <c r="G24" s="223"/>
       <c r="H24" s="226"/>
       <c r="I24" s="227"/>
       <c r="J24" s="228"/>
       <c r="K24" s="223"/>
       <c r="L24" s="223"/>
-      <c r="M24" s="299"/>
+      <c r="M24" s="668"/>
       <c r="N24" s="145"/>
       <c r="O24" s="145"/>
       <c r="P24" s="145"/>
@@ -27863,14 +27800,14 @@
       <c r="C25" s="213"/>
       <c r="D25" s="212"/>
       <c r="E25" s="224"/>
-      <c r="F25" s="298"/>
+      <c r="F25" s="667"/>
       <c r="G25" s="223"/>
       <c r="H25" s="226"/>
       <c r="I25" s="227"/>
       <c r="J25" s="228"/>
       <c r="K25" s="223"/>
       <c r="L25" s="223"/>
-      <c r="M25" s="299"/>
+      <c r="M25" s="668"/>
       <c r="N25" s="145"/>
       <c r="O25" s="145"/>
       <c r="P25" s="145"/>
@@ -27890,14 +27827,14 @@
       <c r="C26" s="213"/>
       <c r="D26" s="212"/>
       <c r="E26" s="224"/>
-      <c r="F26" s="298"/>
+      <c r="F26" s="667"/>
       <c r="G26" s="223"/>
       <c r="H26" s="226"/>
       <c r="I26" s="227"/>
       <c r="J26" s="228"/>
       <c r="K26" s="223"/>
       <c r="L26" s="223"/>
-      <c r="M26" s="299"/>
+      <c r="M26" s="668"/>
       <c r="N26" s="145"/>
       <c r="O26" s="145"/>
       <c r="P26" s="145"/>
@@ -27917,14 +27854,14 @@
       <c r="C27" s="213"/>
       <c r="D27" s="212"/>
       <c r="E27" s="224"/>
-      <c r="F27" s="298"/>
+      <c r="F27" s="667"/>
       <c r="G27" s="223"/>
       <c r="H27" s="226"/>
       <c r="I27" s="227"/>
       <c r="J27" s="228"/>
       <c r="K27" s="223"/>
       <c r="L27" s="223"/>
-      <c r="M27" s="299"/>
+      <c r="M27" s="668"/>
       <c r="N27" s="145"/>
       <c r="O27" s="145"/>
       <c r="P27" s="145"/>
@@ -28601,7 +28538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29284,7 +29221,7 @@
       <c r="F4" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="201"/>
+      <c r="G4" s="658"/>
       <c r="H4" s="197"/>
       <c r="I4" s="145"/>
       <c r="J4" s="145"/>
@@ -29347,7 +29284,7 @@
       <c r="F6" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="318" t="s">
+      <c r="G6" s="669" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="145"/>
@@ -29990,12 +29927,12 @@
     <row r="29" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="365"/>
       <c r="B29" s="366"/>
-      <c r="C29" s="367"/>
-      <c r="D29" s="367"/>
-      <c r="E29" s="367"/>
-      <c r="F29" s="367"/>
-      <c r="G29" s="367"/>
-      <c r="H29" s="368"/>
+      <c r="C29" s="670"/>
+      <c r="D29" s="670"/>
+      <c r="E29" s="670"/>
+      <c r="F29" s="670"/>
+      <c r="G29" s="670"/>
+      <c r="H29" s="671"/>
       <c r="I29" s="145"/>
       <c r="J29" s="145"/>
       <c r="K29" s="145"/>
@@ -30017,12 +29954,12 @@
     <row r="30" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="365"/>
       <c r="B30" s="366"/>
-      <c r="C30" s="367"/>
-      <c r="D30" s="367"/>
-      <c r="E30" s="367"/>
-      <c r="F30" s="367"/>
-      <c r="G30" s="367"/>
-      <c r="H30" s="368"/>
+      <c r="C30" s="670"/>
+      <c r="D30" s="670"/>
+      <c r="E30" s="670"/>
+      <c r="F30" s="670"/>
+      <c r="G30" s="670"/>
+      <c r="H30" s="671"/>
       <c r="I30" s="145"/>
       <c r="J30" s="145"/>
       <c r="K30" s="145"/>
@@ -30044,12 +29981,12 @@
     <row r="31" ht="21.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="369"/>
       <c r="B31" s="370"/>
-      <c r="C31" s="371"/>
-      <c r="D31" s="371"/>
-      <c r="E31" s="371"/>
-      <c r="F31" s="371"/>
-      <c r="G31" s="371"/>
-      <c r="H31" s="372"/>
+      <c r="C31" s="672"/>
+      <c r="D31" s="672"/>
+      <c r="E31" s="672"/>
+      <c r="F31" s="672"/>
+      <c r="G31" s="672"/>
+      <c r="H31" s="673"/>
       <c r="I31" s="145"/>
       <c r="J31" s="145"/>
       <c r="K31" s="145"/>
@@ -30416,7 +30353,7 @@
       <c r="F43" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G43" s="318" t="s">
+      <c r="G43" s="669" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="145"/>
